--- a/output/CLOTH01_summer/feeds_excel/simulation feeds/SupplierOrderHeader.xlsx
+++ b/output/CLOTH01_summer/feeds_excel/simulation feeds/SupplierOrderHeader.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-04-08 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-04-09 00:00:00</t>
+          <t>2024-04-08 00:00:00</t>
         </is>
       </c>
     </row>
@@ -574,34 +574,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024-04-08 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240402_DC_01_IBT_000006</t>
+          <t>PO_CLOTH01_20240401_DC_01_000006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-04-02 00:00:00</t>
+          <t>2024-04-01 00:00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024-04-02 00:00:00</t>
+          <t>2024-04-09 00:00:00</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240403_DC_01_IBT_000008</t>
+          <t>PO_CLOTH01_20240402_DC_01_IBT_000008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-03 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024-04-03 00:00:00</t>
+          <t>2024-04-02 00:00:00</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240404_DC_01_IBT_000010</t>
+          <t>PO_CLOTH01_20240403_DC_01_IBT_000010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-04-04 00:00:00</t>
+          <t>2024-04-03 00:00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024-04-04 00:00:00</t>
+          <t>2024-04-03 00:00:00</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240405_DC_01_IBT_000012</t>
+          <t>PO_CLOTH01_20240404_DC_01_IBT_000012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-04-05 00:00:00</t>
+          <t>2024-04-04 00:00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024-04-05 00:00:00</t>
+          <t>2024-04-04 00:00:00</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240406_DC_01_IBT_000014</t>
+          <t>PO_CLOTH01_20240405_DC_01_IBT_000014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04-06 00:00:00</t>
+          <t>2024-04-05 00:00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024-04-06 00:00:00</t>
+          <t>2024-04-05 00:00:00</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240407_DC_01_IBT_000016</t>
+          <t>PO_CLOTH01_20240406_DC_01_IBT_000016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-04-07 00:00:00</t>
+          <t>2024-04-06 00:00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024-04-07 00:00:00</t>
+          <t>2024-04-06 00:00:00</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240408_DC_01_IBT_000018</t>
+          <t>PO_CLOTH01_20240407_DC_01_IBT_000018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-08 00:00:00</t>
+          <t>2024-04-07 00:00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024-04-08 00:00:00</t>
+          <t>2024-04-07 00:00:00</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240408_DC_01_000020</t>
+          <t>PO_CLOTH01_20240408_DC_01_IBT_000020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -969,17 +969,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-08 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2024-04-16 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1553,27 +1553,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240415_DC_01_000042</t>
+          <t>PO_CLOTH01_20240416_DC_01_IBT_000042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2024-04-16 00:00:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-16 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240416_DC_01_IBT_000044</t>
+          <t>PO_CLOTH01_20240417_DC_01_IBT_000044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-17 00:00:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-17 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240417_DC_01_IBT_000046</t>
+          <t>PO_CLOTH01_20240418_DC_01_IBT_000046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-17 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024-04-17 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240418_DC_01_IBT_000048</t>
+          <t>PO_CLOTH01_20240419_DC_01_IBT_000048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-04-18 00:00:00</t>
+          <t>2024-04-19 00:00:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024-04-18 00:00:00</t>
+          <t>2024-04-19 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240419_DC_01_IBT_000050</t>
+          <t>PO_CLOTH01_20240420_DC_01_IBT_000050</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-04-19 00:00:00</t>
+          <t>2024-04-20 00:00:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2024-04-19 00:00:00</t>
+          <t>2024-04-20 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240420_DC_01_IBT_000052</t>
+          <t>PO_CLOTH01_20240421_DC_01_IBT_000052</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-04-20 00:00:00</t>
+          <t>2024-04-21 00:00:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2024-04-20 00:00:00</t>
+          <t>2024-04-21 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1877,12 +1877,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240421_DC_01_IBT_000054</t>
+          <t>PO_CLOTH01_20240422_DC_01_IBT_000054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04-21 00:00:00</t>
+          <t>2024-04-22 00:00:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2024-04-21 00:00:00</t>
+          <t>2024-04-22 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240422_DC_01_IBT_000056</t>
+          <t>PO_CLOTH01_20240422_DC_01_000056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1941,17 +1941,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-30 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2024-04-30 00:00:00</t>
+          <t>2024-04-29 00:00:00</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2024-04-29 00:00:00</t>
+          <t>2024-05-09 00:00:00</t>
         </is>
       </c>
     </row>
@@ -2032,73 +2032,73 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2024-05-09 00:00:00</t>
+          <t>2024-04-30 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240422_DC_01_000060</t>
+          <t>PO_CLOTH01_20240423_DC_01_IBT_000060</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2024-04-30 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240422_DC_01_000061</t>
+          <t>PO_CLOTH01_20240423_DC_01_IBT_000061</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2024-04-29 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240423_DC_01_IBT_000062</t>
+          <t>PO_CLOTH01_20240424_DC_01_IBT_000062</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-24 00:00:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2113,19 +2113,19 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-24 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240423_DC_01_IBT_000063</t>
+          <t>PO_CLOTH01_20240424_DC_01_IBT_000063</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-24 00:00:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2140,19 +2140,19 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-24 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240424_DC_01_IBT_000064</t>
+          <t>PO_CLOTH01_20240425_DC_01_IBT_000064</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04-24 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2167,19 +2167,19 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2024-04-24 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240424_DC_01_IBT_000065</t>
+          <t>PO_CLOTH01_20240425_DC_01_IBT_000065</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-04-24 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2194,19 +2194,19 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-04-24 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240425_DC_01_IBT_000066</t>
+          <t>PO_CLOTH01_20240426_DC_01_IBT_000066</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240425_DC_01_IBT_000067</t>
+          <t>PO_CLOTH01_20240426_DC_01_IBT_000067</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2248,19 +2248,19 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240426_DC_01_IBT_000068</t>
+          <t>PO_CLOTH01_20240427_DC_01_IBT_000068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2275,19 +2275,19 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240426_DC_01_IBT_000069</t>
+          <t>PO_CLOTH01_20240427_DC_01_IBT_000069</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2302,19 +2302,19 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240427_DC_01_IBT_000070</t>
+          <t>PO_CLOTH01_20240428_DC_01_IBT_000070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-28 00:00:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2329,19 +2329,19 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-28 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PO_CLOTH01_20240427_DC_01_IBT_000071</t>
+          <t>PO_CLOTH01_20240428_DC_01_IBT_000071</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-28 00:00:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2355,60 +2355,6 @@
         </is>
       </c>
       <c r="E72" t="inlineStr">
-        <is>
-          <t>2024-04-27 00:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>PO_CLOTH01_20240428_DC_01_IBT_000072</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2024-04-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2024-04-28 00:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>PO_CLOTH01_20240428_DC_01_IBT_000073</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2024-04-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
         <is>
           <t>2024-04-28 00:00:00</t>
         </is>
